--- a/EstablecimientoSalud/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/EstablecimientoSalud/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>1321</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>40119</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE TARUCANI</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-16.32152491</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>1328</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>40108</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-16.48952679</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>1276</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-16.43449</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>1290</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>40124</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>UCHUMAYO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-16.430706</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>1254</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>40128</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>YURA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-16.25090344</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>1304</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>40102</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ALTO SELVA ALEGRE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-16.37633305</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>40129</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-16.45004288</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>25066</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-16.4176097</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>1259</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-16.445535</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>23488</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>40129</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-16.44374056</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>1378</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>40120</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SANTA ISABEL DE SIGUAS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-16.27925769</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>1302</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>40102</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ALTO SELVA ALEGRE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-16.3666543</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>1279</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-16.46142333</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>1295</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>40109</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MARIANO MELGAR</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-16.40465083</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>23338</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-16.4569563</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>1318</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-16.40793389</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>7722</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>40109</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MARIANO MELGAR</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-16.39311429</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>1317</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-16.40950532</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>13306</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>40125</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>VITOR</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-16.4678697</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>1291</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>40102</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ALTO SELVA ALEGRE</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-16.38123178</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>1294</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>40109</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MARIANO MELGAR</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-16.401929</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>1298</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-16.4130014</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>1323</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>40125</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>VITOR</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-16.58611246</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>1273</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-16.44873667</t>
@@ -1970,40 +1850,35 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>1329</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>40108</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-16.42200395</t>
@@ -2032,40 +1907,35 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>1249</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-16.39405746</t>
@@ -2094,40 +1964,35 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>1288</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>40113</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>POCSI</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-16.5179115</t>
@@ -2156,40 +2021,35 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>27464</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>40103</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CAYMA</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-16.3426764</t>
@@ -2218,40 +2078,35 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>34970</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-16.4408759</t>
@@ -2280,40 +2135,35 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>1332</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>40108</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-16.68625167</t>
@@ -2342,40 +2192,35 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>1333</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>40108</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-16.57853458</t>
@@ -2404,40 +2249,35 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>1337</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>40120</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>SANTA ISABEL DE SIGUAS</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-16.20651208</t>
@@ -2466,40 +2306,35 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>1238</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-16.38917198</t>
@@ -2528,40 +2363,35 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>1292</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>40110</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-16.383061</t>
@@ -2590,40 +2420,35 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>40102</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ALTO SELVA ALEGRE</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-16.36894101</t>
@@ -2652,40 +2477,35 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>1310</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-16.41573556</t>
@@ -2714,40 +2534,35 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>1260</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>40123</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>TIABAYA</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-16.45055632</t>
@@ -2776,40 +2591,35 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>1261</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>40105</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>CHARACATO</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-16.46839351</t>
@@ -2838,40 +2648,35 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>1271</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-16.47323411</t>
@@ -2900,40 +2705,35 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>1313</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-16.43390621</t>
@@ -2962,40 +2762,35 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>1307</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>40110</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>-16.371812</t>
@@ -3024,40 +2819,35 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>1251</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>40103</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>CAYMA</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>-16.32804293</t>
@@ -3086,40 +2876,35 @@
       <c r="K43" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>6890</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>40103</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>CAYMA</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>-16.33187701</t>
@@ -3148,40 +2933,35 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>31488</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>-16.4478087</t>
@@ -3210,40 +2990,35 @@
       <c r="K45" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>1272</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>40129</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>-16.43492124</t>
@@ -3272,40 +3047,35 @@
       <c r="K46" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>36495</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>40108</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-16.6101643</t>
@@ -3334,40 +3104,35 @@
       <c r="K47" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>1320</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>40106</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>CHIGUATA</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-16.38296096</t>
@@ -3396,40 +3161,35 @@
       <c r="K48" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>40125</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>VITOR</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>-16.52432968</t>
@@ -3458,40 +3218,35 @@
       <c r="K49" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>40124</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>UCHUMAYO</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>-16.451012</t>
@@ -3520,40 +3275,35 @@
       <c r="K50" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>1262</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>40114</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>POLOBAYA</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>-16.56658739</t>
@@ -3582,40 +3332,35 @@
       <c r="K51" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>13297</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>40101</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>-16.39531833</t>
@@ -3644,40 +3389,35 @@
       <c r="K52" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>1293</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>40110</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>-16.395062</t>
@@ -3706,40 +3446,35 @@
       <c r="K53" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-16.39811426</t>
@@ -3768,40 +3503,35 @@
       <c r="K54" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>1233</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>40126</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>-16.38601829</t>
@@ -3830,40 +3560,35 @@
       <c r="K55" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>1299</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>40106</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>CHIGUATA</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>-16.40277486</t>
@@ -3892,40 +3617,35 @@
       <c r="K56" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>-16.32541994</t>
@@ -3954,40 +3674,35 @@
       <c r="K57" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>1248</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>-16.38425942</t>
@@ -4016,40 +3731,35 @@
       <c r="K58" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>1263</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>40129</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>-16.43296376</t>
@@ -4078,40 +3788,35 @@
       <c r="K59" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>1267</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>40129</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>-16.42567922</t>
@@ -4140,40 +3845,35 @@
       <c r="K60" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>1270</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>-16.45366513</t>
@@ -4202,40 +3902,35 @@
       <c r="K61" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>12459</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>-16.3825985</t>
@@ -4264,40 +3959,35 @@
       <c r="K62" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>1308</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>40109</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>MARIANO MELGAR</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>-16.397108</t>
@@ -4326,40 +4016,35 @@
       <c r="K63" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>11448</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>-16.35071237</t>
@@ -4388,40 +4073,35 @@
       <c r="K64" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>32056</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>40110</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>-16.38666903</t>
@@ -4450,40 +4130,35 @@
       <c r="K65" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>36180</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>40101</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>-16.41398755</t>
@@ -4512,40 +4187,35 @@
       <c r="K66" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>1316</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>-16.40853203</t>
@@ -4574,40 +4244,35 @@
       <c r="K67" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>1236</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>-16.37727084</t>
@@ -4636,40 +4301,35 @@
       <c r="K68" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>1281</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>40124</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>UCHUMAYO</t>
-        </is>
-      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>-16.444755</t>
@@ -4698,40 +4358,35 @@
       <c r="K69" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>1289</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>40113</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>POCSI</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>-16.5178854</t>
@@ -4760,40 +4415,35 @@
       <c r="K70" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>1274</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>-16.4504</t>
@@ -4822,40 +4472,35 @@
       <c r="K71" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>1244</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>40103</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>CAYMA</t>
-        </is>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>-16.36180621</t>
@@ -4884,40 +4529,35 @@
       <c r="K72" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>1253</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>40128</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>YURA</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>-16.30516833</t>
@@ -4946,40 +4586,35 @@
       <c r="K73" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>1237</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>-16.3514378</t>
@@ -5008,40 +4643,35 @@
       <c r="K74" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>1327</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>40108</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>LA JOYA</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>-16.44527906</t>
@@ -5070,40 +4700,35 @@
       <c r="K75" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>7744</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>-16.41811878</t>
@@ -5132,40 +4757,35 @@
       <c r="K76" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>1319</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>40119</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE TARUCANI</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>-16.18404701</t>
@@ -5194,40 +4814,35 @@
       <c r="K77" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>27843</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>-16.3773032</t>
@@ -5256,40 +4871,35 @@
       <c r="K78" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>15310</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>-16.41505355</t>
@@ -5318,40 +4928,35 @@
       <c r="K79" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>40110</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>-16.37658833</t>
@@ -5380,40 +4985,35 @@
       <c r="K80" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>1312</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>-16.4189014</t>
@@ -5442,40 +5042,35 @@
       <c r="K81" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>1315</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>-16.42725308</t>
@@ -5504,40 +5099,35 @@
       <c r="K82" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>1297</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>-16.41757353</t>
@@ -5566,40 +5156,35 @@
       <c r="K83" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>1301</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>40102</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ALTO SELVA ALEGRE</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>-16.37005787</t>
@@ -5628,40 +5213,35 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>1309</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>40109</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>MARIANO MELGAR</t>
-        </is>
-      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>-16.40120964</t>
@@ -5690,40 +5270,35 @@
       <c r="K85" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>1268</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>-16.44741132</t>
@@ -5752,40 +5327,35 @@
       <c r="K86" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>13307</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>40110</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>-16.3955181</t>
@@ -5814,40 +5384,35 @@
       <c r="K87" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>1300</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>40102</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>ALTO SELVA ALEGRE</t>
-        </is>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>-16.37219268</t>
@@ -5876,40 +5441,35 @@
       <c r="K88" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>1269</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>SOCABAYA</t>
-        </is>
-      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>-16.44747911</t>
@@ -5938,40 +5498,35 @@
       <c r="K89" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>1334</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>40125</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>VITOR</t>
-        </is>
-      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>-16.37286167</t>
@@ -6000,40 +5555,35 @@
       <c r="K90" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>1275</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>-16.44025167</t>
@@ -6062,40 +5612,35 @@
       <c r="K91" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>1277</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>40107</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>JACOBO HUNTER</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>-16.455345</t>
@@ -6124,40 +5669,35 @@
       <c r="K92" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>1305</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>40110</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>MIRAFLORES</t>
-        </is>
-      </c>
       <c r="F93" t="inlineStr">
         <is>
           <t>-16.37569833</t>
@@ -6186,40 +5726,35 @@
       <c r="K93" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>1257</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>40129</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>JOSE LUIS BUSTAMANTE Y RIVERO</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>-16.44440828</t>
@@ -6248,40 +5783,35 @@
       <c r="K94" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>1283</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>40117</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>SACHACA</t>
-        </is>
-      </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>-16.41128147</t>
@@ -6310,40 +5840,35 @@
       <c r="K95" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>1335</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>40121</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>SANTA RITA DE SIGUAS</t>
-        </is>
-      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>-16.488805</t>
@@ -6372,40 +5897,35 @@
       <c r="K96" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>17845</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>CERRO COLORADO</t>
-        </is>
-      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>-16.35082301</t>
@@ -6434,40 +5954,35 @@
       <c r="K97" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>1286</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>40115</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>QUEQUEÑA</t>
-        </is>
-      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>-16.55676342</t>
@@ -6496,40 +6011,35 @@
       <c r="K98" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>11664</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>PAUCARPATA</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>-16.4256037</t>
@@ -6558,40 +6068,35 @@
       <c r="K99" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>040101</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>16336</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>40101</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>-16.4045887</t>
@@ -6620,11 +6125,6 @@
       <c r="K100" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>040101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/EstablecimientoSalud/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
